--- a/experiments/nrp_sat_pairwise_exp_results.xlsx
+++ b/experiments/nrp_sat_pairwise_exp_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,30 +447,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -498,16 +488,10 @@
         <v>32.3935</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32.3935</v>
-      </c>
-      <c r="I2" t="n">
         <v>5002.2</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -531,16 +515,10 @@
         <v>31.9932</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>31.9932</v>
-      </c>
-      <c r="I3" t="n">
         <v>5022.5</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -564,16 +542,10 @@
         <v>32.2098</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>32.2098</v>
-      </c>
-      <c r="I4" t="n">
         <v>5047.9</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -597,16 +569,10 @@
         <v>32.0937</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>32.0937</v>
-      </c>
-      <c r="I5" t="n">
         <v>5025.4</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -630,16 +596,10 @@
         <v>32.1011</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>32.1011</v>
-      </c>
-      <c r="I6" t="n">
         <v>5017.9</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -663,16 +623,10 @@
         <v>32.1895</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>32.1895</v>
-      </c>
-      <c r="I7" t="n">
         <v>5041.6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -696,16 +650,10 @@
         <v>32.9063</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>32.9063</v>
-      </c>
-      <c r="I8" t="n">
         <v>5048.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -729,16 +677,10 @@
         <v>32.4301</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>32.4301</v>
-      </c>
-      <c r="I9" t="n">
         <v>5001</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -762,16 +704,10 @@
         <v>32.4715</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>32.4715</v>
-      </c>
-      <c r="I10" t="n">
         <v>5013.9</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -795,16 +731,10 @@
         <v>31.786</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>31.786</v>
-      </c>
-      <c r="I11" t="n">
         <v>5023.8</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -830,16 +760,10 @@
         <v>32.25747</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>32.25747</v>
-      </c>
-      <c r="I12" t="n">
         <v>5024.48</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,30 +807,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -934,16 +848,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
         <v>5001.9</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -967,16 +875,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
         <v>5070.5</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,16 +902,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
         <v>5045.9</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1033,16 +929,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>5067.8</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1066,16 +956,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
         <v>5010.9</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1099,16 +983,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
         <v>5078.4</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1132,16 +1010,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
         <v>5055.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1165,16 +1037,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
         <v>5068.9</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1198,16 +1064,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
         <v>5034.1</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1231,16 +1091,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
         <v>5005.3</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1266,16 +1120,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
         <v>5043.929999999999</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,30 +1167,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1370,16 +1208,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
         <v>5079.8</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1403,16 +1235,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
         <v>5010.5</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1436,16 +1262,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
         <v>5080</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1469,16 +1289,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>5061.2</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1502,16 +1316,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
         <v>5046.2</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1535,16 +1343,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
         <v>5018.3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1568,16 +1370,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
         <v>5047.4</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1601,16 +1397,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
         <v>5051.8</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,16 +1424,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
         <v>5016.2</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,16 +1451,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
         <v>5058.8</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1702,16 +1480,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
         <v>5047.02</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,30 +1527,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1806,16 +1568,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
         <v>5034.6</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1839,16 +1595,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
         <v>5062.2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1872,16 +1622,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
         <v>5050.5</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1905,16 +1649,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>5049</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1938,16 +1676,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
         <v>5053.5</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1971,16 +1703,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
         <v>5028.6</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2004,16 +1730,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
         <v>5032.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2037,16 +1757,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
         <v>5053.1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2070,16 +1784,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
         <v>5072.8</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2103,16 +1811,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
         <v>5051.4</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2138,16 +1840,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
         <v>5048.830000000001</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
